--- a/diseases/d031/2010-2014.xlsx
+++ b/diseases/d031/2010-2014.xlsx
@@ -1288,9 +1288,6 @@
       <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.006151406726758049</v>
       </c>
@@ -1959,9 +1956,6 @@
       <c r="O9" t="n">
         <v>18</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.0369084403605483</v>
       </c>
@@ -2630,9 +2624,6 @@
       <c r="O13" t="n">
         <v>12</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.0246056269070322</v>
       </c>
@@ -3301,9 +3292,6 @@
       <c r="O17" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.0205046890891935</v>
       </c>
@@ -3972,9 +3960,6 @@
       <c r="O21" t="n">
         <v>12</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.0246056269070322</v>
       </c>
@@ -4643,9 +4628,6 @@
       <c r="O25" t="n">
         <v>8</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.0164037512713548</v>
       </c>
@@ -5314,9 +5296,6 @@
       <c r="O29" t="n">
         <v>7</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.01435328236243545</v>
       </c>
@@ -5985,9 +5964,6 @@
       <c r="O33" t="n">
         <v>3</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.006151406726758049</v>
       </c>
@@ -6656,9 +6632,6 @@
       <c r="O37" t="n">
         <v>4</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.0082018756356774</v>
       </c>
@@ -7327,9 +7300,6 @@
       <c r="O41" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -7998,9 +7968,6 @@
       <c r="O45" t="n">
         <v>8</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.0164037512713548</v>
       </c>
@@ -8669,9 +8636,6 @@
       <c r="O49" t="n">
         <v>19</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.03895890926946765</v>
       </c>
@@ -9340,9 +9304,6 @@
       <c r="O53" t="n">
         <v>8</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.01628411100157898</v>
       </c>
@@ -10011,9 +9972,6 @@
       <c r="O57" t="n">
         <v>15</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.03053270812796058</v>
       </c>
@@ -10682,9 +10640,6 @@
       <c r="O61" t="n">
         <v>34</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.06920747175671066</v>
       </c>
@@ -11353,9 +11308,6 @@
       <c r="O65" t="n">
         <v>37</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.07531401338230277</v>
       </c>
@@ -12024,9 +11976,6 @@
       <c r="O69" t="n">
         <v>60</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.1221308325118423</v>
       </c>
@@ -12695,9 +12644,6 @@
       <c r="O73" t="n">
         <v>52</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.1058467215102634</v>
       </c>
@@ -13366,9 +13312,6 @@
       <c r="O77" t="n">
         <v>39</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.07938504113269752</v>
       </c>
@@ -14037,9 +13980,6 @@
       <c r="O81" t="n">
         <v>17</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.03460373587835533</v>
       </c>
@@ -14708,9 +14648,6 @@
       <c r="O85" t="n">
         <v>18</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.03663924975355271</v>
       </c>
@@ -15379,9 +15316,6 @@
       <c r="O89" t="n">
         <v>30</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.06106541625592116</v>
       </c>
@@ -16050,9 +15984,6 @@
       <c r="O93" t="n">
         <v>32</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.06513644400631591</v>
       </c>
@@ -16721,9 +16652,6 @@
       <c r="O97" t="n">
         <v>64</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.1302728880126318</v>
       </c>
@@ -17392,9 +17320,6 @@
       <c r="O101" t="n">
         <v>68</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.1370979364855301</v>
       </c>
@@ -18063,9 +17988,6 @@
       <c r="O105" t="n">
         <v>45</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.09072657561542431</v>
       </c>
@@ -18734,9 +18656,6 @@
       <c r="O109" t="n">
         <v>38</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.07661355274191387</v>
       </c>
@@ -19405,9 +19324,6 @@
       <c r="O113" t="n">
         <v>60</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.1209687674872324</v>
       </c>
@@ -20076,9 +19992,6 @@
       <c r="O117" t="n">
         <v>56</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.1129041829880836</v>
       </c>
@@ -20747,9 +20660,6 @@
       <c r="O121" t="n">
         <v>47</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.09475886786499874</v>
       </c>
@@ -21418,9 +21328,6 @@
       <c r="O125" t="n">
         <v>55</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.1108880368632964</v>
       </c>
@@ -22089,9 +21996,6 @@
       <c r="O129" t="n">
         <v>40</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.08064584499148827</v>
       </c>
@@ -22760,9 +22664,6 @@
       <c r="O133" t="n">
         <v>40</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.08064584499148827</v>
       </c>
@@ -23431,9 +23332,6 @@
       <c r="O137" t="n">
         <v>104</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.2096791969778695</v>
       </c>
@@ -24102,9 +24000,6 @@
       <c r="O141" t="n">
         <v>163</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.3286318183403147</v>
       </c>
@@ -24773,9 +24668,6 @@
       <c r="O145" t="n">
         <v>252</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.5080688234463763</v>
       </c>
@@ -25444,9 +25336,6 @@
       <c r="O149" t="n">
         <v>237</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.4733263193828856</v>
       </c>
@@ -26115,9 +26004,6 @@
       <c r="O153" t="n">
         <v>262</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.5232552560266498</v>
       </c>
@@ -26786,9 +26672,6 @@
       <c r="O157" t="n">
         <v>205</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.4094172804788672</v>
       </c>
@@ -27457,9 +27340,6 @@
       <c r="O161" t="n">
         <v>330</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.6590619636976887</v>
       </c>
@@ -28128,9 +28008,6 @@
       <c r="O165" t="n">
         <v>427</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.8527862378754942</v>
       </c>
@@ -28799,9 +28676,6 @@
       <c r="O169" t="n">
         <v>329</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.6570648062319382</v>
       </c>
@@ -29470,9 +29344,6 @@
       <c r="O173" t="n">
         <v>219</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.4373774849993753</v>
       </c>
@@ -30141,9 +30012,6 @@
       <c r="O177" t="n">
         <v>129</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.2576333130818237</v>
       </c>
@@ -30812,9 +30680,6 @@
       <c r="O181" t="n">
         <v>159</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.3175480370543409</v>
       </c>
@@ -31483,9 +31348,6 @@
       <c r="O185" t="n">
         <v>285</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.5691898777389131</v>
       </c>
@@ -32154,9 +32016,6 @@
       <c r="O189" t="n">
         <v>388</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.7748970967112219</v>
       </c>
@@ -32825,9 +32684,6 @@
       <c r="O193" t="n">
         <v>708</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>1.413987485751405</v>
       </c>
@@ -33496,9 +33352,6 @@
       <c r="O197" t="n">
         <v>560</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>1.108053948495337</v>
       </c>
@@ -34167,9 +34020,6 @@
       <c r="O201" t="n">
         <v>514</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>1.017035231297506</v>
       </c>
@@ -34838,9 +34688,6 @@
       <c r="O205" t="n">
         <v>530</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>1.04869391554023</v>
       </c>
@@ -35509,9 +35356,6 @@
       <c r="O209" t="n">
         <v>556</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>1.100139277434656</v>
       </c>
@@ -36180,9 +36024,6 @@
       <c r="O213" t="n">
         <v>512</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>1.013077895767166</v>
       </c>
@@ -36851,9 +36692,6 @@
       <c r="O217" t="n">
         <v>444</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.878528487735589</v>
       </c>
@@ -37522,9 +37360,6 @@
       <c r="O221" t="n">
         <v>426</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.8429124679625245</v>
       </c>
@@ -38193,9 +38028,6 @@
       <c r="O225" t="n">
         <v>287</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.5678776486038605</v>
       </c>
@@ -38864,9 +38696,6 @@
       <c r="O229" t="n">
         <v>322</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.6371310203848191</v>
       </c>
@@ -39535,9 +39364,6 @@
       <c r="O233" t="n">
         <v>469</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.9279951818648452</v>
       </c>
@@ -40206,9 +40032,6 @@
       <c r="O237" t="n">
         <v>523</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>1.034843241184038</v>
       </c>
@@ -40876,9 +40699,6 @@
       </c>
       <c r="O241" t="n">
         <v>666</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
       </c>
       <c r="R241" t="n">
         <v>1.317792731603384</v>
